--- a/make_table/tuihuo_table.xlsx
+++ b/make_table/tuihuo_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04月26日</t>
+          <t>04月27日</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,23 +496,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4502265372069087501</t>
+          <t>4502296837024046206</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tb55359442</t>
+          <t>thzxlm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>庄园蜜兰500g*1，完好，无礼袋</t>
+          <t>庄园东方红500g*1，拆用（剩98%）；茶巾*1，完好</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>退货</t>
+          <t>换货</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -522,11 +522,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>772060602470173</t>
+          <t>JT3160903068070</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>940.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04月26日</t>
+          <t>04月27日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,18 +545,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2701861394120018984</t>
+          <t>2701828489124026663</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>t_1494908056584_0625</t>
+          <t>宜春邹志明</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>金香鸭屎500g*1，茶侧*1，完好</t>
+          <t>测试*1，完好</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,11 +571,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SF5199054527984</t>
+          <t>极兔速递 JT3159498098520</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>812.12</v>
+        <v>838</v>
       </c>
     </row>
     <row r="4">
@@ -584,7 +584,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04月26日</t>
+          <t>04月27日</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -592,20 +592,12 @@
           <t>天猫</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4502318798045006230</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>蜡笔小新lllx</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>老丛私房4大茶集200g*2，老丛私房鸭屎7g*2，老丛私房杏仁50g*1，岽顶蜜兰7g*1，茶具*1，完好</t>
+          <t>测试*2，损坏</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -620,207 +612,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SF5199015712505</t>
+          <t>73704218931851</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3912.17</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>04月26日</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>天猫</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2701862583092037871</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>chenjil83239311</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>老丛私房八仙100g*1，完好</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>退货</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>口感不合适</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>SF5199653123158</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>779.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>04月26日</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>天猫</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2701831443174028763</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>weihua26685546</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>老丛私房八仙100g*1，庄园鸭屎50g*1，庄园蜜兰50g*1，完好，盒损*1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>退货</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>口感不合适</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>JT3160267097581</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>04月26日</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>天猫</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2701834034063019581</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>weihua26685546</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>老丛私房八仙100g*1，庄园鸭屎50g*1，庄园蜜兰50g*1，完好，盒损*1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>退货</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>口感不合适</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>JT3160267097581</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>260.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>04月26日</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>天猫</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4502280924002020507</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>月凉如水1983</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>浓香芝兰50g*1，拆用（剩70%），无外盒</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>换货</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>口感不合适</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>772060532356228</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>

--- a/make_table/tuihuo_table.xlsx
+++ b/make_table/tuihuo_table.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04月27日</t>
+          <t>04月28日</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,23 +496,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4502296837024046206</t>
+          <t>5112015805018001926</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>thzxlm</t>
+          <t>卢卡娃11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>庄园东方红500g*1，拆用（剩98%）；茶巾*1，完好</t>
+          <t>庄园蜜兰252g*1，清香桂花252g*1，完好</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>换货</t>
+          <t>退货</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -522,11 +522,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>JT3160903068070</t>
+          <t>SF0229073694555</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1037.2</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04月27日</t>
+          <t>04月28日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,18 +545,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2701828489124026663</t>
+          <t>5111273016030019324</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>宜春邹志明</t>
+          <t>jay_89757</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>测试*1，完好</t>
+          <t>庄园蜜兰50g*2，完好</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,11 +571,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>极兔速递 JT3159498098520</t>
+          <t>SF0226053710872</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>838</v>
+        <v>214.4</v>
       </c>
     </row>
     <row r="4">
@@ -584,7 +584,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04月27日</t>
+          <t>04月28日</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -592,12 +592,20 @@
           <t>天猫</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3298694232944009978</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tb062516175225</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>测试*2，损坏</t>
+          <t>庄园东方红500g*1，茶侧*1，茶具*1，完好，罐损</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -612,11 +620,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>73704218931851</t>
+          <t>JT5480183168323</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>838</v>
+        <v>1290.35</v>
       </c>
     </row>
   </sheetData>

--- a/make_table/tuihuo_table.xlsx
+++ b/make_table/tuihuo_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04月28日</t>
+          <t>04月30日</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,18 +496,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5112015805018001926</t>
+          <t>3297702000559001192</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>卢卡娃11</t>
+          <t>瞳孔中的水平线</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>庄园蜜兰252g*1，清香桂花252g*1，完好</t>
+          <t>岽顶蜜兰50g*1，完好，盒损</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -522,11 +522,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SF0229073694555</t>
+          <t>73705853678251</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1037.2</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04月28日</t>
+          <t>04月30日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,18 +545,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5111273016030019324</t>
+          <t>3297183962088001079</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>jay_89757</t>
+          <t>淡杰橙</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>庄园蜜兰50g*2，完好</t>
+          <t>岽顶蜜兰50g*1，完好</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,11 +571,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SF0226053710872</t>
+          <t>772061019165423</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>214.4</v>
+        <v>163.12</v>
       </c>
     </row>
     <row r="4">
@@ -584,7 +584,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04月28日</t>
+          <t>04月30日</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -594,18 +594,18 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3298694232944009978</t>
+          <t>3298257517445020082</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tb062516175225</t>
+          <t>跨海_高速</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>庄园东方红500g*1，茶侧*1，茶具*1，完好，罐损</t>
+          <t>庄园蜜兰50g*1，完好；庄园鸭屎7g*1，压损</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -620,11 +620,354 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>JT5480183168323</t>
+          <t>772061046443705</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1290.35</v>
+        <v>103.14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>04月30日</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5112077292914061845</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bry168</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>清香桂花50g*1，金香鸭屎50g*1，完好</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>退货</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SF5131942141115</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>205.12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04月30日</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4502307746172039543</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tb980163199765</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>老丛私房宋种200g*1，老丛私房杏仁50g*1，完好，无礼袋</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>退货</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SF5131203810768</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>04月30日</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5112297722999098522</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>t_1484586471144_0593</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>老丛私房八仙200g*1，公道杯*1，完好</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>退货</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SF5131080598864</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>04月30日</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3297897193516006882</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>黄昏光影</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>庄园蜜兰50g*1，岽顶蜜兰50g*1，庄园鸭屎7g*1，完好，盒损*2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>退货</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>772060984991552</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>250.14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>04月30日</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4502308394121050815</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>青晕晕</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>金香鸭屎500g*1，茶侧*1，完好</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>退货</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>772060951098059</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>821.34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>04月30日</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4502302884105091802</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>js459649073</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>庄园鸭屎500g*1，庄园鸭屎50g*1，老丛私房鸭屎100g*1，茶具*1，茶侧*1，完好，礼袋损</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>退货</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>772060851430833</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2128.77</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>04月30日</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3297901010220007689</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>花花花啊啊m</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>老丛私房鸭屎100g*1，完好</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>退货</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>772061066393190</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>694.2</v>
       </c>
     </row>
   </sheetData>
